--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_266_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_266_R27.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.41</v>
+        <v>7.1315</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8274</v>
+        <v>5.7842</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5825</v>
+        <v>1.3473</v>
       </c>
       <c r="G2" t="n">
         <v>2.5877</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2473</v>
+        <v>-0.5258</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4832</v>
+        <v>-0.5265</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2359</v>
+        <v>0.0007</v>
       </c>
       <c r="V2" t="n">
         <v>2.2862</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6134</v>
+        <v>4.3171</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5266</v>
+        <v>3.1295</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0868</v>
+        <v>1.1876</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2639</v>
@@ -688,13 +688,13 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1814</v>
+        <v>-0.1149</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5272</v>
+        <v>0.13</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3457</v>
+        <v>-0.2449</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3298</v>
+        <v>3.0855</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.7869</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7355</v>
+        <v>2.2986</v>
       </c>
       <c r="G4" t="n">
         <v>1.0753</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3809</v>
+        <v>0.1366</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4086</v>
+        <v>-0.2159</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7894</v>
+        <v>0.3525</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6778999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7938</v>
+        <v>1.3623</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9783</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1845</v>
+        <v>0.632</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2023</v>
+        <v>1.268</v>
       </c>
       <c r="H5" t="n">
-        <v>0.982</v>
+        <v>-0.7093</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7796999999999999</v>
+        <v>1.9773</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0031</v>
+        <v>3.6521</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3612</v>
+        <v>-0.3795</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3581</v>
+        <v>4.0316</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8008</v>
+        <v>-2.3841</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3792</v>
+        <v>-0.3298</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4216</v>
+        <v>-2.0543</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1097</v>
+        <v>-0.0501</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9752</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1344</v>
+        <v>0.4646</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8672</v>
+        <v>1.1698</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5377</v>
+        <v>1.1527</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3295</v>
+        <v>0.0172</v>
       </c>
       <c r="G6" t="n">
-        <v>1.268</v>
+        <v>0.2023</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7093</v>
+        <v>0.982</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9773</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6521</v>
+        <v>1.0031</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3795</v>
+        <v>1.3612</v>
       </c>
       <c r="L6" t="n">
-        <v>4.0316</v>
+        <v>-0.3581</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3841</v>
+        <v>-0.8008</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3298</v>
+        <v>-0.3792</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0543</v>
+        <v>-0.4216</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5452</v>
+        <v>0.4856</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7073</v>
+        <v>0.1496</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1621</v>
+        <v>0.3361</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.5984</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0952</v>
+        <v>-1.5055</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1711</v>
+        <v>2.1039</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4844</v>
@@ -1000,13 +1000,13 @@
         <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4577</v>
+        <v>0.0648</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1202</v>
+        <v>-0.5305</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6625</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.3943</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0884</v>
+        <v>-0.7778</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0643</v>
+        <v>1.3749</v>
       </c>
       <c r="F8" t="n">
         <v>-2.1527</v>
@@ -1078,10 +1078,10 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.6093</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4481</v>
+        <v>-0.1375</v>
       </c>
       <c r="U8" t="n">
         <v>-0.4718</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7067</v>
+        <v>-1.4544</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2491</v>
+        <v>-2.1311</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5423</v>
+        <v>0.6768</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4872</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7556</v>
+        <v>-0.5032</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3822</v>
+        <v>-0.2478</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2851</v>
+        <v>-2.3352</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8224</v>
+        <v>-1.7045</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4627</v>
+        <v>-0.6307</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9149</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2104</v>
+        <v>-0.2605</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7468</v>
+        <v>-0.6289</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5364</v>
+        <v>0.3684</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6696</v>
+        <v>-2.4515</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7057</v>
+        <v>-1.0976</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9639</v>
+        <v>-1.3539</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.824</v>
+        <v>0.6832</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5089</v>
+        <v>-1.9567</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3151</v>
+        <v>2.6399</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9302</v>
+        <v>3.0852</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0168</v>
+        <v>-1.502</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.947</v>
+        <v>4.5872</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8938</v>
+        <v>-2.402</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.4547</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.368</v>
+        <v>-1.9473</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.5111</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>-0.7035</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3062</v>
+        <v>0.1924</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8383</v>
+        <v>-2.7704</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2156</v>
+        <v>-0.7057</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6228</v>
+        <v>-2.0647</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6832</v>
+        <v>-1.824</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9567</v>
+        <v>-0.5089</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6399</v>
+        <v>-1.3151</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0852</v>
+        <v>-0.9302</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.502</v>
+        <v>0.0168</v>
       </c>
       <c r="L12" t="n">
-        <v>4.5872</v>
+        <v>-0.947</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.402</v>
+        <v>-0.8938</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4547</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.9473</v>
+        <v>-0.368</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0876</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8979</v>
+        <v>-0.0187</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8215</v>
+        <v>-0.224</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0764</v>
+        <v>0.2054</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.501899999999999</v>
+        <v>7.875299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.440599999999998</v>
+        <v>5.814100000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>2.061100000000001</v>
+        <v>2.0614</v>
       </c>
       <c r="G13" t="n">
-        <v>2.122099999999999</v>
+        <v>2.1221</v>
       </c>
       <c r="H13" t="n">
         <v>-3.4149</v>
@@ -1459,7 +1459,7 @@
         <v>-11.3254</v>
       </c>
       <c r="P13" t="n">
-        <v>5.798899999999998</v>
+        <v>5.7989</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.7575</v>
@@ -1468,22 +1468,22 @@
         <v>18.5564</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2799</v>
+        <v>-1.9066</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.8307</v>
+        <v>-3.4573</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5508</v>
+        <v>1.5509</v>
       </c>
       <c r="V13" t="n">
         <v>1.8608</v>
       </c>
       <c r="W13" t="n">
-        <v>6.716799999999999</v>
+        <v>6.7168</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.856000000000001</v>
+        <v>-4.856</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9371</v>
+        <v>4.9885</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8787</v>
+        <v>2.2325</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0585</v>
+        <v>2.756</v>
       </c>
       <c r="G14" t="n">
         <v>1.0235</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7692</v>
+        <v>0.8206</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2082</v>
+        <v>0.1456</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9774</v>
+        <v>0.675</v>
       </c>
       <c r="V14" t="n">
         <v>2.6805</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6129</v>
+        <v>2.4277</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2469</v>
+        <v>4.1289</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.634</v>
+        <v>-1.7012</v>
       </c>
       <c r="G15" t="n">
         <v>3.4466</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0244</v>
+        <v>0.8393</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2873</v>
+        <v>0.1693</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7372</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9304</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1291</v>
+        <v>1.5502</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8148</v>
+        <v>1.1687</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3143</v>
+        <v>0.3815</v>
       </c>
       <c r="G16" t="n">
         <v>2.2953</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5605</v>
+        <v>-0.1395</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1123</v>
+        <v>-0.7585</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5518</v>
+        <v>0.619</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0951</v>
+        <v>1.3646</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5935</v>
+        <v>1.8294</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4983</v>
+        <v>-0.4647</v>
       </c>
       <c r="G17" t="n">
         <v>0.6993</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1639</v>
+        <v>0.4334</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1652</v>
+        <v>0.4011</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0013</v>
+        <v>0.0323</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9658</v>
+        <v>0.8784</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7267</v>
+        <v>-0.3038</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2391</v>
+        <v>1.1822</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2599</v>
+        <v>-0.7119</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4873</v>
+        <v>-0.2736</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2275</v>
+        <v>-0.4383</v>
       </c>
       <c r="J18" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.1245</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0371</v>
+        <v>0.1379</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0368</v>
+        <v>-0.0134</v>
       </c>
       <c r="M18" t="n">
-        <v>0.186</v>
+        <v>-0.8364</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4502</v>
+        <v>-0.4116</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2643</v>
+        <v>-0.4248</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3116</v>
+        <v>-0.0334</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8125</v>
+        <v>-0.4283</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4991</v>
+        <v>0.3949</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4408</v>
+        <v>-0.3139</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5397</v>
+        <v>-0.2169</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9806</v>
+        <v>-0.097</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7119</v>
+        <v>0.2599</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2736</v>
+        <v>0.4873</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4383</v>
+        <v>-0.2275</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1245</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1379</v>
+        <v>0.0371</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0134</v>
+        <v>0.0368</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8364</v>
+        <v>0.186</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4116</v>
+        <v>0.4502</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4248</v>
+        <v>-0.2643</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4709</v>
+        <v>1.0319</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6642</v>
+        <v>0.8689</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1933</v>
+        <v>0.163</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7813</v>
+        <v>-1.2867</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0427</v>
+        <v>-1.5145</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2614</v>
+        <v>0.2278</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3904</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2175</v>
+        <v>-0.288</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0351</v>
+        <v>-0.507</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2526</v>
+        <v>0.219</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7997</v>
+        <v>-2.1701</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7209</v>
+        <v>-1.9568</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0788</v>
+        <v>-0.2133</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2435</v>
@@ -2092,13 +2092,13 @@
         <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.3106</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2513</v>
+        <v>-0.4872</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9322</v>
+        <v>0.7978</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3247</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3518</v>
+        <v>-3.2338</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.548</v>
+        <v>-1.4301</v>
       </c>
       <c r="F22" t="n">
         <v>-1.8037</v>
@@ -2170,10 +2170,10 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3892</v>
+        <v>-0.2713</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U22" t="n">
         <v>0.0589</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3566</v>
+        <v>-3.9026</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6052</v>
+        <v>-0.4873</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.7514</v>
+        <v>-3.4153</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0579</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9946</v>
+        <v>-0.5406</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6642</v>
+        <v>-0.5463</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3304</v>
+        <v>0.0057</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.3932</v>
+        <v>-7.8041</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.865</v>
+        <v>-5.5112</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5282</v>
+        <v>-2.2929</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1042</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4722</v>
+        <v>0.1169</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4323</v>
+        <v>-0.0784</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.04</v>
+        <v>0.1953</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3943</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.5018</v>
+        <v>-7.501800000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.060900000000001</v>
+        <v>-2.0611</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.4405</v>
+        <v>-5.4406</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1222</v>
@@ -2404,13 +2404,13 @@
         <v>12.7576</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2801</v>
+        <v>2.2799</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5507</v>
+        <v>-1.5509</v>
       </c>
       <c r="U25" t="n">
-        <v>3.830800000000001</v>
+        <v>3.8308</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8608</v>
